--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0006.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0006.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Lúc đầu, ta lo nó có thể gặp nguy hiểm nên để nó lại Bjartr Woods. Nhưng khi nó nhìn ta với ánh mắt buồn ấy, ta không nỡ bỏ nó lại. Thế là cuối cùng ta vẫn mang nó theo.</t>
+          <t>Lúc đầu, tao lo nó có thể gặp nguy hiểm nên để nó lại Bjartr Woods. Nhưng khi nó nhìn tao với ánh mắt buồn ấy, tao không nỡ bỏ nó lại. Thế là cuối cùng tao vẫn mang nó theo.</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Lúc mới đến, ngươi còn chẳng biết đường đi lối về... Ta vẫn nhớ cái cách ngươi hoảng loạn như mới hôm qua. Hay đó cũng là một phần thú vị của quá trình?</t>
+          <t>Lúc mới đến, mày còn chẳng biết đường đi lối về... Tao vẫn nhớ cái cách mày hoảng loạn như mới hôm qua. Hay đó cũng là một phần thú vị của quá trình?</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Haha, nếu không có cậu, ta đã phải ngủ ngoài đường rồi. Giờ thì ta thuộc đường đi lối lại như lòng bàn tay... Đó cũng là một phần của cuộc hành trình, phải không?</t>
+          <t>Haha, nếu không có cậu, tao đã phải ngủ ngoài đường rồi. Giờ thì tao thuộc đường đi lối lại như lòng bàn tay... Đó cũng là một phần của cuộc hành trình, phải không?</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Hmm, Bộ phận Synchronization Resonator - Máy Móc của Khoa Kỹ thuật Exostrider chắc hẳn đã tiến hành những nghiên cứu tương tự rồi. Chúng ta có thể hỏi họ khi trở về.</t>
+          <t>Hmm, Bộ phận Đồng Bộ Hóa Resonator - Máy Móc của Khoa Kỹ thuật Exostrider chắc hẳn đã tiến hành những nghiên cứu tương tự rồi. Chúng ta có thể hỏi họ khi trở về.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>At last, vào một ngày nọ, khi tóc ông đã bạc trắng và đang dẫn một con tuần lộc cơ khí lạc lối trở về Bjartr Woods, một Soliskin xuất hiện và nắm lấy tay ông.</t>
+          <t>Cuối cùng, vào một ngày nọ, khi tóc ông đã bạc trắng và đang dẫn một con tuần lộc cơ khí lạc lối trở về Bjartr Woods, một Soliskin xuất hiện và nắm lấy tay ông.</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>"Chett, khi nào ta mới lấy lại được năm trăm Shell Credits đây?" Vậy là mọi sinh vật thông minh trong thiên hà sẽ biết ngươi vẫn nợ ta năm trăm Shell Credits, haha!</t>
+          <t>"Chett, khi nào tao mới lấy lại được năm trăm Shell Credits đây?" Vậy là mọi sinh vật thông minh trong thiên hà sẽ biết mày vẫn nợ tao năm trăm Shell Credits, haha!</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Huaxu Academy. Với những dấu hiệu phục hồi của Threnody tại Jinzhou, mọi thành bang ở Huanglong đều đang đẩy mạnh nghiên cứu phát triển quân sự. Đất nước cần ta hơn bao giờ hết. Còn kế hoạch của cậu là gì?</t>
+          <t>Học viện Huaxu. Với những dấu hiệu phục hồi của Threnody tại Jinzhou, mọi thành bang ở Huanglong đều đang đẩy mạnh nghiên cứu phát triển quân sự. Đất nước cần ta hơn bao giờ hết. Còn kế hoạch của cậu là gì?</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>7 giờ 30 dậy, rửa mặt thay đồ chưa đầy một phút, ăn sáng trong năm phút, và tuyệt đối không được ăn đồ ngọt… Phải từ bỏ đường mới trở thành Synchronist sao?</t>
+          <t>7 giờ 30 dậy, rửa mặt thay đồ chưa đầy một phút, ăn sáng trong năm phút, và tuyệt đối không được ăn đồ ngọt… Phải từ bỏ đường mới trở thành Đồng Bộ Giả sao?</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Department Vật Chất Hư Không chuyên nghiên cứu Hiện Tượng Xói Mòn Sóng và Void Storm để dự đoán và kiểm soát những thảm họa này. Nhưng một khi đã đắm chìm vào nghiên cứu, họ thường quên ăn và... dần đánh mất nhân tính.</t>
+          <t>Cục Vật Chất Hư Không chuyên nghiên cứu Hiện Tượng Xói Mòn Sóng và Bão Hư Không để dự đoán và kiểm soát những thảm họa này. Nhưng một khi đã đắm chìm vào nghiên cứu, họ thường quên ăn và... dần đánh mất nhân tính.</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Đây là giải đấu chiến đấu cơ khí do Câu lạc bộ Sinh cơ tổ chức! Những tín đồ của Exoswarm rất mê mẩn trò này. À, tên đầy đủ của họ là "Câu lạc bộ Nghiên cứu Exoswarm Material Cơ sinh học." Dài kinh khủng, phải không?</t>
+          <t>Đây là giải đấu chiến đấu cơ khí do Câu lạc bộ Sinh cơ tổ chức! Những tín đồ của Exoswarm rất mê mẩn trò này. À, tên đầy đủ của họ là "Câu lạc bộ Nghiên cứu Vật liệu Exoswarm Cơ sinh học." Dài kinh khủng, phải không?</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Còn về Void Storm, bộ đồ bảo hộ sẽ giúp ngăn chặn sự ô nhiễm, và mỗi đội nghiên cứu đều được trang bị những màn hình giám sát tối tân. Họ thường phát hiện dấu hiệu cảnh báo từ sớm.</t>
+          <t>Còn về Bão Hư Không, bộ đồ bảo hộ sẽ giúp ngăn chặn sự ô nhiễm, và mỗi đội nghiên cứu đều được trang bị những màn hình giám sát tối tân. Họ thường phát hiện dấu hiệu cảnh báo từ sớm.</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Ồ, mình chỉ muốn kết hợp một chút thêu phong cách Huanglong, thêm chút xu hướng may đo mới nhất của Ragunna, và một chút gợi ý từ phong cách techwear của New Federation thôi…</t>
+          <t>Ồ, mình chỉ muốn kết hợp một chút thêu phong cách Huanglong, thêm chút xu hướng may đo mới nhất của Ragunna, và một chút gợi ý từ phong cách techwear của Liên Bang Mới thôi…</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Cô ấy sắp đạt đến ngưỡng tự nhận thức rồi, năng lực tính toán của cô ấy đang ở ngay ngưỡng "test người-máy". Nếu hỏi tôi, cô ấy chính là kỳ tích sinh ra từ dữ liệu và mã code!</t>
+          <t>Cô ấy sắp đạt đến ngưỡng tự nhận thức rồi, năng lực tính toán của cô ấy đang ở ngay ngưỡng "kiểm tra người-máy". Nếu hỏi tôi, cô ấy chính là kỳ tích sinh ra từ dữ liệu và mã code!</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Vậy là đàn em của tôi lại đạt được đột phá lớn trong lĩnh vực nghiên cứu của chính tôi trước tôi, và tôi thì chẳng thể tạo ra kết quả mới nào... Thế nên đành phải thu xếp đồ đạc mà gia nhập Pioneer Association thôi.</t>
+          <t>Vậy là đàn em của tôi lại đạt được đột phá lớn trong lĩnh vực nghiên cứu của chính tôi trước tôi, và tôi thì chẳng thể tạo ra kết quả mới nào... Thế nên đành phải thu xếp đồ đạc mà gia nhập Hiệp Hội Tiên Phong thôi.</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>May mắn là Pioneer Association hợp tác chặt chẽ với Học viện. Nhờ sự giới thiệu của người hướng dẫn, ta đã quay lại giảng dạy, dẫn dắt sinh viên và tiếp tục nghiên cứu của mình.</t>
+          <t>May mắn là Hiệp hội Pioneer hợp tác chặt chẽ với Học viện. Nhờ sự giới thiệu của người hướng dẫn, ta đã quay lại giảng dạy, dẫn dắt sinh viên và tiếp tục nghiên cứu của mình.</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Ui, vẫn còn phải nộp kết quả nuôi cấy "Core Năng Lượng Kết Tinh"... Trời ơi, sao Đại học Rabelle lại bắt học đủ thứ thế? Sao trường học lại khó đến vậy chứ…</t>
+          <t>Ui, vẫn còn phải nộp kết quả nuôi cấy "Lõi Năng Lượng Kết Tinh"... Trời ơi, sao Đại học Rabelle lại bắt học đủ thứ thế? Sao trường học lại khó đến vậy chứ…</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Này, nghe đây. Đường vận chuyển tới vùng băng giá đã bị phong tỏa, còn Void Storm thì gây nhiễu liên lạc của Học viện. Dù có cố thế nào, cậu cũng không liên lạc được với họ đâu.</t>
+          <t>Này, nghe đây. Đường vận chuyển tới vùng băng giá đã bị phong tỏa, còn Bão Hư Không thì gây nhiễu liên lạc của Học viện. Dù có cố thế nào, cậu cũng không liên lạc được với họ đâu.</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Nhưng chúng ta có thể nói chuyện với Chủ tịch Lucilla. Bà ấy cũng đến từ Liên bang New. Với nguồn lực bà ấy có ở Học viện và khu vực xung quanh, có lẽ bà ấy có thể giúp cậu liên lạc với gia đình.</t>
+          <t>Nhưng chúng ta có thể nói chuyện với Chủ tịch Lucilla. Bà ấy cũng đến từ Liên bang Mới. Với nguồn lực bà ấy có ở Học viện và khu vực xung quanh, có lẽ bà ấy có thể giúp cậu liên lạc với gia đình.</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Bộ ảnh đó có bố cục sắc bén và cách xử lý ánh sáng, bóng tối cực kỳ độc đáo... Phong cách cá nhân rất đậm Dodget. Xem ảnh của anh ấy là cách tốt nhất để hiểu thế nào là một cảnh quay tuyệt vời và ánh sáng hoàn hảo!</t>
+          <t>Bộ ảnh đó có bố cục sắc bén và cách xử lý ánh sáng, bóng tối cực kỳ độc đáo... Phong cách cá nhân rất đậm nét. Xem ảnh của anh ấy là cách tốt nhất để hiểu thế nào là một cảnh quay tuyệt vời và ánh sáng hoàn hảo!</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>...Khi sứ giả của Nữ Thần Wisdom mang theo dòng trăng thứ bảy, móng vuốt sư tử con sẽ lại khắc dấu lên mê cung. Những người giữ chìa khóa, hãy mở cửa và dệt nên vận mệnh của họ...</t>
+          <t>...Khi sứ giả của Nữ Thần Trí Tuệ mang theo dòng trăng thứ bảy, móng vuốt sư tử con sẽ lại khắc dấu lên mê cung. Những người giữ chìa khóa, hãy mở cửa và dệt nên vận mệnh của họ...</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Nói thẳng ra đi... lần này ngươi làm hỏng xe máy đến mức nào rồi? Đừng có mà tưởng phòng thí nghiệm của ta hoạt động bằng thiện chí. Nếu ta cứ tiếp tục xin thêm kinh phí, Viện sẽ nghi ngờ mất thôi.</t>
+          <t>Nói thẳng ra đi... lần này mày làm hỏng xe máy đến mức nào rồi? Đừng có mà tưởng phòng thí nghiệm của tao hoạt động bằng thiện chí. Nếu tao cứ tiếp tục xin thêm kinh phí, Viện sẽ nghi ngờ mất thôi.</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Thế là ta cải tiến lá chắn khổng lồ của Mechascout thành vật liệu giáp đặc biệt cho khung máy, tạo ra một "Lớp Vô Hiệu Hóa Tuyệt Đối Toàn Thân"...</t>
+          <t>Thế là tao cải tiến lá chắn khổng lồ của Mechascout thành vật liệu giáp đặc biệt cho khung máy, tạo ra một "Lớp Vô Hiệu Hóa Tuyệt Đối Toàn Thân"...</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>From now on, hãy đào sâu nghiên cứu theo hướng này nhé! Ta có linh cảm năm nay ngươi nhất định sẽ giành giải Golden Machine Awards của Khoa Kỹ Thuật đấy!</t>
+          <t>Từ giờ trở đi, hãy đào sâu nghiên cứu theo hướng này nhé! Tao có linh cảm năm nay mày nhất định sẽ giành giải Golden Machine Awards của Khoa Kỹ Thuật đấy!</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Mỗi cỗ máy đều được lập trình sẵn các chỉ thị. Like gen và bản năng của con người, chúng tôi đã trao cho chúng "bản năng" riêng dựa trên giao thức này. Ví dụ như...</t>
+          <t>Mỗi cỗ máy đều được lập trình sẵn các chỉ thị. Giống như gen và bản năng của con người, chúng tôi đã trao cho chúng "bản năng" riêng dựa trên giao thức này. Ví dụ như...</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Nếu ai đó thay thế phần lớn cơ thể bằng bộ phận cơ khí, hoặc mang những đặc điểm Discord rõ rệt... và nếu định nghĩa "con người" thay đổi, họ sẽ phán xét như thế nào?</t>
+          <t>Nếu ai đó thay thế phần lớn cơ thể bằng bộ phận cơ khí, hoặc mang những đặc điểm Tacet Discord rõ rệt... và nếu định nghĩa "con người" thay đổi, họ sẽ phán xét như thế nào?</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Hiện hình đi! Shield Bất Diệt của Ideals! À, đừng để ý, đó chỉ là mật mã mở khóa ta đặt thôi... Nào, hãy dốc hết sức đi! Nếu phá được, ta sẽ chịu trách nhiệm!</t>
+          <t>Hiện hình đi! Khiên Bất Diệt của Lý Tưởng! À, đừng để ý, đó chỉ là mật mã mở khóa ta đặt thôi... Nào, hãy dốc hết sức đi! Nếu phá được, ta sẽ chịu trách nhiệm!</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Tất cả hàng hóa nhập vào đều được đưa lên thang máy chính của Riseway lên sân ga hàng hóa. Không gì có thể đến Viện Nghiên Cứu hay Học viện mà không qua sự kiểm tra của ta.</t>
+          <t>Tất cả hàng hóa nhập vào đều được đưa lên thang máy chính của Riseway lên sân ga hàng hóa. Không gì có thể đến Viện Nghiên cứu hay Học viện mà không qua sự kiểm tra của ta.</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Giờ hy vọng của ta đặt vào công nghệ của Spacetrek Collective để xác nhận sự tồn tại của sinh vật đó... Ta muốn nghe tin tức về nó ngay khi tìm thấy. Đó là lý do ta sống ở đây.</t>
+          <t>Giờ hy vọng của ta đặt vào công nghệ của Tập Đoàn Spacetrek để xác nhận sự tồn tại của sinh vật đó... Ta muốn nghe tin tức về nó ngay khi tìm thấy. Đó là lý do ta sống ở đây.</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Ground đã được đào để xây dựng Trạm Nghiên cứu Cực, rồi sau đó là nền móng cho thang máy chở hàng khổng lồ gắn trên lưỡi kiếm của Exostrider – Starward Riseway...</t>
+          <t>Mặt đất đã được đào để xây dựng Trạm Nghiên cứu Cực, rồi sau đó là nền móng cho thang máy chở hàng khổng lồ gắn trên lưỡi kiếm của Exostrider – Starward Riseway...</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Ta nghe nói trên Diễn đàn Học viện có mục "Make-A-Wish" ấy nhỉ? Hohoho! Thời thế đổi thay rồi. Ông già này cũng biết dùng Terminal đấy chứ!</t>
+          <t>Ta nghe nói trên Diễn đàn Học viện có mục "Make-A-Wish" ấy nhỉ? Hohoho! Thời thế đổi thay rồi. Ông già này cũng biết dùng Thiết bị đầu cuối đấy chứ!</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Hehe, tham gia đoàn thám hiểm đến vùng băng giá chắc là trải nghiệm khó quên nhất kể từ khi tôi đến Echo này… Chắc sau khi về, tôi sẽ còn suy nghĩ mãi về những gì đã thấy ở đây.</t>
+          <t>Hehe, tham gia đoàn thám hiểm đến vùng băng giá chắc là trải nghiệm khó quên nhất kể từ khi tôi đến Tổ Tacet này… Chắc sau khi về, tôi sẽ còn suy nghĩ mãi về những gì đã thấy ở đây.</t>
         </is>
       </c>
     </row>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Void Storm là lĩnh vực nghiên cứu của ta. Mỗi khi phát hiện sự dao động năng lượng mạnh ở đâu, ta lập tức lao đến hiện trường để ghi lại hình thái nguyên sơ của tai họa ngay trước khi nó bùng phát.</t>
+          <t>Bão Hư Không là lĩnh vực nghiên cứu của ta. Mỗi khi phát hiện sự dao động năng lượng mạnh ở đâu, ta lập tức lao đến hiện trường để ghi lại hình thái nguyên sơ của tai họa ngay trước khi nó bùng phát.</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Ta từng nghĩ mình là loại người hợp với cô độc—hướng nội, trầm lặng, không sợ buồn chán. Mãi cho đến khi đến Lahai-Roi, ta mới nhận ra cái "cô độc" mà ta biết chỉ là một ảo tưởng lãng mạn rỗng tuếch.</t>
+          <t>Tao từng nghĩ mình là loại người hợp với cô độc—hướng nội, trầm lặng, không sợ buồn chán. Mãi cho đến khi đến Lahai-Roi, tao mới nhận ra cái "cô độc" mà tao biết chỉ là một ảo tưởng lãng mạn rỗng tuếch.</t>
         </is>
       </c>
     </row>
@@ -12747,7 +12747,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Nhưng gần đây, Học viện dường như đã phát hiện ra một Synchronist khác với thành tích xuất sắc trên mọi mặt. Name gì ấy nhỉ...? {PlayerName}, hình như vậy...</t>
+          <t>Nhưng gần đây, Học viện dường như đã phát hiện ra một Synchronist khác với thành tích xuất sắc trên mọi mặt. Tên gì ấy nhỉ...? {PlayerName}, hình như vậy...</t>
         </is>
       </c>
     </row>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Các trưởng lão bộ tộc Roya kể rằng nơi này từng là một vùng đất tràn đầy vẻ đẹp thiên nhiên. Nhưng rồi Lament từ trên trời giáng xuống... biến nó thành vùng đất chết chóc như thế này.</t>
+          <t>Các trưởng lão bộ tộc Roya kể rằng nơi này từng là một vùng đất tràn đầy vẻ đẹp thiên nhiên. Nhưng rồi Lời Than Vãn từ trên trời giáng xuống... biến nó thành vùng đất chết chóc như thế này.</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>...Nhưng nói đến chuyện đó, khi về tới nơi, ta phải dành thời gian cảm ơn cả đội mới được. Nhiều người trong số họ tốt nghiệp Startorch Academy, nên họ biết về Lahai-Roi rõ hơn ta nhiều.</t>
+          <t>...Nhưng nói đến chuyện đó, khi về tới nơi, ta phải dành thời gian cảm ơn cả đội mới được. Nhiều người trong số họ tốt nghiệp Học viện Startorch, nên họ biết về Lahai-Roi rõ hơn ta nhiều.</t>
         </is>
       </c>
     </row>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Hahaha, lần đầu ai đến đây cũng thế cả. Khoan về nhà, ta sẽ làm món gì đó cho cậu. Món này nấu chín mới ngon. Nấu canh thì ngon không tưởng luôn.</t>
+          <t>Hahaha, lần đầu ai đến đây cũng thế cả. Đợi về nhà, ta sẽ làm món gì đó cho cậu. Món này nấu chín mới ngon. Nấu canh thì ngon không tưởng luôn.</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Nhìn những vết nhăn trên trang giấy, những cuốn sách này đã được đọc từ đầu đến cuối. Còn "Những Dodget Văn hóa Thế Giới Căn Bản"... thì có vẻ chưa bao giờ được mở ra.</t>
+          <t>Nhìn những vết nhăn trên trang giấy, những cuốn sách này đã được đọc từ đầu đến cuối. Còn "Những nét Văn hóa Thế Giới Căn Bản"... thì có vẻ chưa bao giờ được mở ra.</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Chưa hết đâu! Ta còn ghi lại những lời phàn nàn về căng tin, S.I.G.M.A. phạt tốc độ, tiếng la hoảng của giáo viên và học viên khi thiết bị trục trặc...</t>
+          <t>Chưa hết đâu! Tao còn ghi lại những lời phàn nàn về căng tin, S.I.G.M.A. phạt tốc độ, tiếng la hoảng của giáo viên và học viên khi thiết bị trục trặc...</t>
         </is>
       </c>
     </row>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>(Thì thầm) Chào cậu, rất vui được gặp! Mình là Ignatius, đến từ New Federation. Mình thích nghiên cứu Khoa học Vật Chất Hư Không! Cậu có muốn làm bạn không? Mình có thể mời cậu ăn s-s-s-s-s-sa-lát!</t>
+          <t>(Thì thầm) Chào cậu, rất vui được gặp! Mình là Ignatius, đến từ Liên Bang Mới. Mình thích nghiên cứu Khoa học Vật Chất Hư Không! Cậu có muốn làm bạn không? Mình có thể mời cậu ăn s-s-s-s-s-sa-lát!</t>
         </is>
       </c>
     </row>
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>(Thì thầm) Chào cậu, rất vui được gặp! Mình là Ignatius, đến từ New Federation. Mình thích nghiên cứu Khoa học Vật Chất Hư Không! Cậu có muốn làm bạn không? Mình có thể mời cậu ăn s-s-s-s-s-sa-lát!</t>
+          <t>(Thì thầm) Chào cậu, rất vui được gặp! Mình là Ignatius, đến từ Liên Bang Mới. Mình thích nghiên cứu Khoa học Vật Chất Hư Không! Cậu có muốn làm bạn không? Mình có thể mời cậu ăn s-s-s-s-s-sa-lát!</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>(Thì thầm) Chào cậu, rất vui được gặp! Mình là Ignatius, đến từ New Federation. Mình thích nghiên cứu Khoa học Vật Chất Hư Không! Cậu có muốn làm bạn không? Mình có thể mời cậu ăn s-s-s-s-s-sa-lát!</t>
+          <t>(Thì thầm) Chào cậu, rất vui được gặp! Mình là Ignatius, đến từ Liên Bang Mới. Mình thích nghiên cứu Khoa học Vật Chất Hư Không! Cậu có muốn làm bạn không? Mình có thể mời cậu ăn s-s-s-s-s-sa-lát!</t>
         </is>
       </c>
     </row>
@@ -20319,7 +20319,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Đây là một quang phổ kỳ lạ, dễ dàng kích hoạt sự hòa quyện giác quan nơi người nghe. Bên kia Etheric Seaic, bụi sao trôi dạt, sóng vô tuyến tán loạn... Đó là không gian sâu thẳm, nơi nền văn minh từng đặt chân tới.</t>
+          <t>Đây là một quang phổ kỳ lạ, dễ dàng kích hoạt sự hòa quyện giác quan nơi người nghe. Bên kia Biển Etheric, bụi sao trôi dạt, sóng vô tuyến tán loạn... Đó là không gian sâu thẳm, nơi nền văn minh từng đặt chân tới.</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Nhưng sáng hôm sau, thủ tục nhập môn của hắn vào Viện Nghiên Cứu đã được đẩy nhanh và hoàn tất. Từ đó, hắn luân chuyển qua các dự án mật. Không ai còn thấy hắn xuất hiện trước công chúng nữa.</t>
+          <t>Nhưng sáng hôm sau, thủ tục nhập môn của hắn vào Viện Nghiên cứu đã được đẩy nhanh và hoàn tất. Từ đó, hắn luân chuyển qua các dự án mật. Không ai còn thấy hắn xuất hiện trước công chúng nữa.</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Impressive. Không ngờ lại có người vượt tường lửa, hack vào hệ thống để farm điểm. May mà Hội Student đã thiết lập hệ thống phòng thủ động...</t>
+          <t>Ấn tượng. Không ngờ lại có người vượt tường lửa, hack vào hệ thống để farm điểm. May mà Hội Học sinh đã thiết lập hệ thống phòng thủ động...</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Lựa chọn sáng suốt đấy. Cậu có thể làm việc cho Hội Student trong giờ phục vụ, và sẽ được cộng điểm sau khi hoàn thành. Cậu rảnh không? Bộ phận An Ninh Thông Tin đang thiếu người.</t>
+          <t>Lựa chọn sáng suốt đấy. Cậu có thể làm việc cho Hội Học sinh trong giờ phục vụ, và sẽ được cộng điểm sau khi hoàn thành. Cậu rảnh không? Bộ phận An Ninh Thông Tin đang thiếu người.</t>
         </is>
       </c>
     </row>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Đúng, họ không phải đối phó với mấy con TARD-E, nhưng Exoswarm và Soliskin chỉ là một phần trong cuộc sống hàng ngày của họ. Đừng bắt ta kể về mấy cái bùa Royan và vỏ số học của họ nữa...</t>
+          <t>Đúng, họ không phải đối phó với mấy con TARD-E, nhưng Exoswarm và Soliskin chỉ là một phần trong cuộc sống hàng ngày của họ. Đừng bắt tao kể về mấy cái bùa Royan và vỏ số học của họ nữa...</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Cậu có xem New Solar Celebration không? Đám sinh viên các khoa khác xếp hàng dài để thử buồng mô phỏng, rồi nôn khắp nơi. Đẹp tuyệt!</t>
+          <t>Cậu có xem Lễ Hội Mặt Trời Mới không? Đám sinh viên các khoa khác xếp hàng dài để thử buồng mô phỏng, rồi nôn khắp nơi. Đẹp tuyệt!</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Nghe này, xin lỗi nhé. Tại ta không giải được câu đố ấy. Lúc đó tâm trạng không tốt, nên mới cáu lên. À, và... xin lỗi vì đã dọa biến ngươi thành cái máy chuyển động vĩnh cửu kích hoạt bằng âm thanh với Zip Zaps và cột đèn đấy.</t>
+          <t>Nghe này, xin lỗi nhé. Tại tao không giải được câu đố ấy. Lúc đó tâm trạng không tốt, nên mới cáu lên. À, và... xin lỗi vì đã dọa biến mày thành cái máy chuyển động vĩnh cửu kích hoạt bằng âm thanh với Zip Zaps và cột đèn đấy.</t>
         </is>
       </c>
     </row>
@@ -21619,7 +21619,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Mà ta phải nói thật... Dạy Kronapuff luyện nhận thức chẳng khác nào đổ công vô ích. Nó còn chẳng phân biệt được gel năng lượng với tạp chí. Chỉ biết thử hết mọi cách để moi mẩu bánh mì từ cậu thôi!</t>
+          <t>Mà tao phải nói thật... Dạy Kronapuff luyện nhận thức chẳng khác nào đổ công vô ích. Nó còn chẳng phân biệt được gel năng lượng với tạp chí. Chỉ biết thử hết mọi cách để moi mẩu bánh mì từ cậu thôi!</t>
         </is>
       </c>
     </row>
@@ -22009,7 +22009,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Khoan tý, đây là tin nhắn tự động: "Kính gửi học viên, hệ thống phát hiện thiếu tài liệu sự kiện trong đơn đăng ký của bạn. Vui lòng tải và điền mẫu đơn, sau đó gửi về..."</t>
+          <t>Đợi tý, đây là tin nhắn tự động: "Kính gửi học viên, hệ thống phát hiện thiếu tài liệu sự kiện trong đơn đăng ký của bạn. Vui lòng tải và điền mẫu đơn, sau đó gửi về..."</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Thành tích xuất sắc, lễ phép, lại còn xung phong trong cơn Void Storm. Được yêu mến là phải rồi. Nhưng bỏ học... Tớ có gợi ý rồi. Con bé bảo chưa nghĩ tới, muốn suy nghĩ kỹ trước khi quyết định.</t>
+          <t>Thành tích xuất sắc, lễ phép, lại còn xung phong trong cơn Bão Hư Không. Được yêu mến là phải rồi. Nhưng bỏ học... Tớ có gợi ý rồi. Con bé bảo chưa nghĩ tới, muốn suy nghĩ kỹ trước khi quyết định.</t>
         </is>
       </c>
     </row>
@@ -22464,7 +22464,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Khi Core Phản Ứng cháy rực trong thân thể Baldur, ánh sáng hấp hối sẽ nhuộm mái vòm Lahai-Ro trong hoàng hôn rực lửa, thiêu đốt tất cả thành tro tàn. Đây sẽ là trận chiến cuối cùng, không đường lui.</t>
+          <t>Khi Lõi Phản Ứng cháy rực trong thân thể Baldur, ánh sáng hấp hối sẽ nhuộm mái vòm Lahai-Ro trong hoàng hôn rực lửa, thiêu đốt tất cả thành tro tàn. Đây sẽ là trận chiến cuối cùng, không đường lui.</t>
         </is>
       </c>
     </row>
@@ -22529,7 +22529,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Yes. Việc Helios phóng thành công... và thay thế Động cơ Phản ứng làm mặt trời của Lahai-Roi hoàn toàn phản ánh sự chuyển giao giữa Kỷ nguyên Lò Phản ứng Thánh và Kỷ nguyên Chạng vạng.</t>
+          <t>Đúng vậy. Việc Helios phóng thành công... và thay thế Động cơ Phản ứng làm mặt trời của Lahai-Roi hoàn toàn phản ánh sự chuyển giao giữa Kỷ nguyên Lò Phản ứng Thánh và Kỷ nguyên Chạng vạng.</t>
         </is>
       </c>
     </row>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Sự thức tỉnh của Hvedrungr... báo hiệu sự trở lại của Threnodian. Những cơn Void Storm xuất hiện dày đặc gần đây có thể coi là điềm báo trước cho lời tiên tri này.</t>
+          <t>Sự thức tỉnh của Hvedrungr... báo hiệu sự trở lại của Threnodian. Những cơn Bão Hư Không xuất hiện dày đặc gần đây có thể coi là điềm báo trước cho lời tiên tri này.</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Chỉ có một nhà nghiên cứu tình cờ tìm thấy thẻ căn cước tại nơi cô ấy từng giao tranh với vài Tacet Discord. Dịch từ ngôn ngữ Lahai-Roi, dòng chữ ghi—"Special Response Force Ứng Phó".</t>
+          <t>Chỉ có một nhà nghiên cứu tình cờ tìm thấy thẻ căn cước tại nơi cô ấy từng giao tranh với vài Tacet Discord. Dịch từ ngôn ngữ Lahai-Roi, dòng chữ ghi—"Lực Lượng Đặc Nhiệm Ứng Phó".</t>
         </is>
       </c>
     </row>
@@ -22988,7 +22988,7 @@
       <c r="M346" t="inlineStr">
         <is>
           <t>Thời tiết: Nắng
-Log: Hệ thống bình thường
+Nhật ký: Hệ thống bình thường
 Tôi không giỏi viết mấy cái này. Nhưng tháng trước, khi tôi không nộp... cô ấy có vẻ buồn.
 Chắc thế này là đủ số từ rồi. Mọi thứ đều ổn. Đừng lo, tôi sẽ đảm bảo mọi thứ vẫn ổn.</t>
         </is>
@@ -23120,7 +23120,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Hay cô ấy đã ký kết một thỏa thuận nào đó với Collective? Chẳng hạn… cô không muốn ai khác bị tổn thương, nên quyết định Special Response Force chỉ cần có mình cô thôi.</t>
+          <t>Hay cô ấy đã ký kết một thỏa thuận nào đó với Collective? Chẳng hạn… cô không muốn ai khác bị tổn thương, nên quyết định Lực Lượng Đặc Nhiệm chỉ cần có mình cô thôi.</t>
         </is>
       </c>
     </row>
@@ -23396,7 +23396,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>À, một sinh viên từ Học viện Rabelle... Hello, tôi là Peregrine, giám sát xây dựng trạm căn cứ. Cậu đi cùng đoàn thám hiểm phải không? Phiền nếu tôi hỏi vài câu được không?</t>
+          <t>À, một sinh viên từ Học viện Rabelle... Xin chào, tôi là Peregrine, giám sát xây dựng trạm căn cứ. Cậu đi cùng đoàn thám hiểm phải không? Phiền nếu tôi hỏi vài câu được không?</t>
         </is>
       </c>
     </row>
@@ -24371,7 +24371,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Á—Ư—Ư— Ha ha! Thầy quá khen rồi, Giáo sư Zhenhong. Theo đuổi chân lý, dạy dỗ học trò... Đây chỉ là nhiệm vụ của mọi giảng viên trẻ tại Startorch Academy thôi mà...</t>
+          <t>Á—Ư—Ư— Ha ha! Thầy quá khen rồi, Giáo sư Zhenhong. Theo đuổi chân lý, dạy dỗ học trò... Đây chỉ là nhiệm vụ của mọi giảng viên trẻ tại Học viện Startorch thôi mà...</t>
         </is>
       </c>
     </row>
@@ -24436,7 +24436,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Cô ấy muốn vào Startorch Academy à... Để tôi chuẩn bị một số tài liệu. Tôi sẽ gửi cho cậu. Còn lại... sao ta không đợi đến khi Lumen Initiative kết thúc? Tôi sẽ dẫn cả hai đi tham quan Học viện!</t>
+          <t>Cô ấy muốn vào Học viện Startorch à... Để tôi chuẩn bị một số tài liệu. Tôi sẽ gửi cho cậu. Còn lại... sao ta không đợi đến khi Lumen Initiative kết thúc? Tôi sẽ dẫn cả hai đi tham quan Học viện!</t>
         </is>
       </c>
     </row>
@@ -24826,7 +24826,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>...Tôi không chắc đó là quyết định đúng đắn. Dimmr Plains khắc nghiệt hơn nhiều so với các vùng khác, nhưng những loài động vật này không hề trên bờ vực tuyệt chủng. Chúng thậm chí còn đang phát triển mạnh mẽ...</t>
+          <t>...Tôi không chắc đó là quyết định đúng đắn. Đồng Bằng Dimmr khắc nghiệt hơn nhiều so với các vùng khác, nhưng những loài động vật này không hề trên bờ vực tuyệt chủng. Chúng thậm chí còn đang phát triển mạnh mẽ...</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Cảm ơn Giáo sư Melvie ạ. Con rất biết ơn tất cả sự giúp đỡ mà thầy đã dành cho con. Con đã học hỏi được rất nhiều khi làm việc cùng đội, và Core Năng Lượng Kết Tinh là một lĩnh vực con thực sự đam mê...</t>
+          <t>Cảm ơn Giáo sư Melvie ạ. Con rất biết ơn tất cả sự giúp đỡ mà thầy đã dành cho con. Con đã học hỏi được rất nhiều khi làm việc cùng đội, và Lõi Năng Lượng Kết Tinh là một lĩnh vực con thực sự đam mê...</t>
         </is>
       </c>
     </row>
@@ -25346,7 +25346,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hehe, đúng là thế rồi. Đợi tới đó là biết ngay. Đường đua gần vực Dimmr Deep ấy! Gió thổi mang theo tiếng khóc than của những người bị Void Storm cuốn đi. Này, có hứng không, tham gia một cuộc đua không?</t>
+          <t>Hehe, đúng là thế rồi. Đợi tới đó là biết ngay. Đường đua gần vực Dimmr Deep ấy! Gió thổi mang theo tiếng khóc than của những người bị Bão Hư Không cuốn đi. Này, có hứng không, tham gia một cuộc đua không?</t>
         </is>
       </c>
     </row>
@@ -25411,7 +25411,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Ô-Ôi, không thấy cậu ở đó, {PlayerName}! Ehehe... Từ khi thấy bức ảnh cậu đuổi theo Voidworm bằng xe máy thám hiểm, cháu đã trở thành fan cuồng rồi!</t>
+          <t>Ô-Ôi, không thấy bạn ở đó, {PlayerName}! Ehehe... Từ khi thấy bức ảnh bạn đuổi theo Voidworm bằng xe máy thám hiểm, cháu đã trở thành fan cuồng rồi!</t>
         </is>
       </c>
     </row>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Với người mới... Let's see... À, có đấy! Đầu tiên, luôn chụp từ góc thấp. Góc chụp càng thấp càng tốt... Sau đó, khi chỉnh sửa, giảm độ phơi sáng và bão hòa, rồi làm tối vùng sáng...</t>
+          <t>Với người mới... Để xem nào... À, có đấy! Đầu tiên, luôn chụp từ góc thấp. Góc chụp càng thấp càng tốt... Sau đó, khi chỉnh sửa, giảm độ phơi sáng và bão hòa, rồi làm tối vùng sáng...</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Bao nhiêu lần ta phải nhắc ngươi sắp xếp đồ đạc cho gọn? Dụng cụ chính xác và bộ lấy mẫu thì cho vào lớp chống sốc. Bộ cứu thương và lương khô? Để riêng. Đồ dùng thường xuyên? Lớp ngoài. Và thiết bị liên lạc thì phải đeo trên người...</t>
+          <t>Bao nhiêu lần tao phải nhắc mày sắp xếp đồ đạc cho gọn? Dụng cụ chính xác và bộ lấy mẫu thì cho vào lớp chống sốc. Bộ cứu thương và lương khô? Để riêng. Đồ dùng thường xuyên? Lớp ngoài. Và thiết bị liên lạc thì phải đeo trên người...</t>
         </is>
       </c>
     </row>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Vì ngươi, Spacetrek Collective sẽ hỗ trợ mọi việc trong khả năng. Nếu cần gì, cứ liên hệ trực tiếp với người phụ trách. Ngươi cũng có thể bỏ qua quy trình kiểm tra an ninh vận chuyển tiêu chuẩn.</t>
+          <t>Vì ngươi, Tập Đoàn Spacetrek sẽ hỗ trợ mọi việc trong khả năng. Nếu cần gì, cứ liên hệ trực tiếp với người phụ trách. Ngươi cũng có thể bỏ qua quy trình kiểm tra an ninh vận chuyển tiêu chuẩn.</t>
         </is>
       </c>
     </row>
@@ -26646,7 +26646,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Công việc của chúng ta được chia thành ba lĩnh vực: đặc tính và ứng dụng của Exoswarm, nghiên cứu lý thuyết về đặc tính của Voidmatter, và Sáng kiến Thám hiểm Etheric Seaic.</t>
+          <t>Công việc của chúng ta được chia thành ba lĩnh vực: đặc tính và ứng dụng của Exoswarm, nghiên cứu lý thuyết về đặc tính của Voidmatter, và Sáng kiến Thám hiểm Biển Etheric.</t>
         </is>
       </c>
     </row>
@@ -26776,7 +26776,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Về nghiên cứu tính chất của Vật Chất Hư Không, những cuộc chạm trán với Aleph-1 và Resonator liên quan đã cho chúng tôi nhận ra rằng Vật Chất Hư Không sở hữu những đặc tính chưa được biết đến. Đây sẽ là một trong những trọng tâm chính của Department Vật Chất Hư Không trong thời gian tới.</t>
+          <t>Về nghiên cứu tính chất của Vật Chất Hư Không, những cuộc chạm trán với Aleph-1 và Resonator liên quan đã cho chúng tôi nhận ra rằng Vật Chất Hư Không sở hữu những đặc tính chưa được biết đến. Đây sẽ là một trong những trọng tâm chính của Cục Vật Chất Hư Không trong thời gian tới.</t>
         </is>
       </c>
     </row>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Tất cả khu vực dự án tại Viện Nghiên Cứu Spacetrek Collective hiện đang mở cửa cho du khách. Chúng tôi chỉ yêu cầu các vị đừng làm phiền các nhà nghiên cứu khi họ đang tiến hành thí nghiệm. Điều đó đôi khi có thể dẫn đến... những hậu quả không lường trước được.</t>
+          <t>Tất cả khu vực dự án tại Viện Nghiên cứu Spacetrek Collective hiện đang mở cửa cho du khách. Chúng tôi chỉ yêu cầu các vị đừng làm phiền các nhà nghiên cứu khi họ đang tiến hành thí nghiệm. Điều đó đôi khi có thể dẫn đến... những hậu quả không lường trước được.</t>
         </is>
       </c>
     </row>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Đặt giả thuyết, thiết kế thí nghiệm, thu thập dữ liệu trong lúc Dodge Void Storm. Kết quả lại chẳng có gì đáng kể. Điều chỉnh thông số. Phát hiện một điểm dị thường. Rồi mất ba tháng trời cố giải thích đống số liệu của chính mình...</t>
+          <t>Đặt giả thuyết, thiết kế thí nghiệm, thu thập dữ liệu trong lúc né tránh Bão Hư Không. Kết quả lại chẳng có gì đáng kể. Điều chỉnh thông số. Phát hiện một điểm dị thường. Rồi mất ba tháng trời cố giải thích đống số liệu của chính mình...</t>
         </is>
       </c>
     </row>
@@ -27166,7 +27166,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Dự án "không cần thiết" nghĩa là sao? Nói rõ cho tôi biết, định nghĩa của anh về điều đó là gì? Khảo sát Dimmr Plains gần đây khắc nghiệt đến mức chúng ta đã mất mấy đội khảo sát rồi. Không thay thế thì lấy dữ liệu từ trên trời à?</t>
+          <t>Dự án "không cần thiết" nghĩa là sao? Nói rõ cho tôi biết, định nghĩa của anh về điều đó là gì? Khảo sát Đồng Bằng Dimmr gần đây khắc nghiệt đến mức chúng ta đã mất mấy đội khảo sát rồi. Không thay thế thì lấy dữ liệu từ trên trời à?</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Và đội của cậu... Cậu thật sự cần nhiều Tacetite đến thế để phủ pha sao? Trời ơi... lại thêm đơn nữa à? Cậu định ăn Tacetite thay cơm à? Rốt cuộc các người đang làm gì ở Dimmr Plains vậy?</t>
+          <t>Và đội của cậu... Cậu thật sự cần nhiều Tacetite đến thế để phủ pha sao? Trời ơi... lại thêm đơn nữa à? Cậu định ăn Tacetite thay cơm à? Rốt cuộc các người đang làm gì ở Đồng Bằng Dimmr vậy?</t>
         </is>
       </c>
     </row>
@@ -27296,7 +27296,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Trong Terminal, cậu tìm thấy một tập tin chứa đường đua mô phỏng cùng bảng thành tích đua xe. Trên bảng xếp hạng, chưa ai từng hoàn thành 80% đường đua.</t>
+          <t>Trong Thiết bị đầu cuối, cậu tìm thấy một tập tin chứa đường đua mô phỏng cùng bảng thành tích đua xe. Trên bảng xếp hạng, chưa ai từng hoàn thành 80% đường đua.</t>
         </is>
       </c>
     </row>
@@ -27361,7 +27361,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>(Hmm? Terminal này có giao diện giống hệt mấy cái do Department Kỹ thuật phát triển. Nhưng mình tưởng họ chỉ nghiên cứu Exostrider thôi. Sao lại làm Terminal cho đua xe máy nhỉ?)</t>
+          <t>(Hmm? Thiết bị đầu cuối này có giao diện giống hệt mấy cái do Cục Kỹ thuật phát triển. Nhưng mình tưởng họ chỉ nghiên cứu Exostrider thôi. Sao lại làm Thiết bị đầu cuối cho đua xe máy nhỉ?)</t>
         </is>
       </c>
     </row>
@@ -27426,7 +27426,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ánh mắt cậu đang nói với ta, "Ta chưa chịu thua đâu." Đừng lo, ta đã biên tập một đoạn giới thiệu ngắn cho cậu, có thể nó sẽ giúp cậu tìm ra cách chinh phục đường đua!</t>
+          <t>Ánh mắt cậu đang nói với ta, "Tao chưa chịu thua đâu." Đừng lo, ta đã biên tập một đoạn giới thiệu ngắn cho cậu, có thể nó sẽ giúp cậu tìm ra cách chinh phục đường đua!</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27491,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Đó là lý do tôi có được Terminal này và tạo ra cuộc đua này. Nhưng tôi gặp chút trục trặc kỹ thuật, nên kết nối chỉ kích hoạt từ xa khi có người cán đích. Haha.</t>
+          <t>Đó là lý do tôi có được Thiết bị đầu cuối này và tạo ra cuộc đua này. Nhưng tôi gặp chút trục trặc kỹ thuật, nên kết nối chỉ kích hoạt từ xa khi có người cán đích. Haha.</t>
         </is>
       </c>
     </row>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Sau khi có quyền truy cập, cậu có thể bắt đầu tái thiết mạng lưới tuyến đường. Điều đó sẽ giúp ích rất nhiều cho Spacetrek Observatory, và cũng giúp việc di chuyển quanh Lahai-Roi dễ dàng hơn cho cậu.</t>
+          <t>Sau khi có quyền truy cập, cậu có thể bắt đầu tái thiết mạng lưới tuyến đường. Điều đó sẽ giúp ích rất nhiều cho Đài Thiên Văn Spacetrek, và cũng giúp việc di chuyển quanh Lahai-Roi dễ dàng hơn cho cậu.</t>
         </is>
       </c>
     </row>
@@ -27818,7 +27818,7 @@
       <c r="M420" t="inlineStr">
         <is>
           <t>Cậu thấy đấy, để nâng cấp Bộ Xây Dựng Đường, cần ba loại vật liệu:
-Mechanite và Đá Nền Cô Đặc làm nguyên liệu thô, cộng thêm một Core Bộ Xây Dựng làm nguồn năng lượng.</t>
+Mechanite và Đá Nền Cô Đặc làm nguyên liệu thô, cộng thêm một Lõi Bộ Xây Dựng làm nguồn năng lượng.</t>
         </is>
       </c>
     </row>
@@ -27883,7 +27883,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Hội Spacetrek Collective từng dùng nó để quan sát và ghi lại mọi hoạt động trong khu vực. Nhưng một cơn Void Storm đã ập đến cách đây vài năm, biến nơi này thành đống đổ nát. Việc sửa chữa... chậm đến mức phải nói là rùa bò.</t>
+          <t>Hội Tập Đoàn Spacetrek từng dùng nó để quan sát và ghi lại mọi hoạt động trong khu vực. Nhưng một cơn Bão Hư Không đã ập đến cách đây vài năm, biến nơi này thành đống đổ nát. Việc sửa chữa... chậm đến mức phải nói là rùa bò.</t>
         </is>
       </c>
     </row>
@@ -28338,7 +28338,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>"{PlayerName}! Cảm ơn rất nhiều vì đã khôi phục mạng lưới đường đi. Mọi người từ khắp nơi ở Lahai-Roi đã đến tiếp tế đồ đạc. Lâu lắm rồi tớ mới được nói chuyện với nhiều người đến thế," Dhalifa nói!</t>
+          <t>"{PlayerName}! Cảm ơn cậu rất nhiều vì đã khôi phục mạng lưới đường đi. Mọi người từ khắp nơi ở Lahai-Roi đã đến tiếp tế đồ đạc. Lâu lắm rồi tớ mới được nói chuyện với nhiều người đến thế," Dhalifa nói!</t>
         </is>
       </c>
     </row>
@@ -28468,7 +28468,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Hừm… Xin lỗi, tôi hơi nghẹn lời. Cảm ơn cậu, {PlayerName}. Chúng tôi chưa bao giờ bỏ cuộc, nhưng nếu không có cậu, có lẽ dự án này sẽ mất hàng năm trời.</t>
+          <t>Hừm… Xin lỗi, tôi hơi nghẹn lời. Cảm ơn bạn, {PlayerName}. Chúng tôi chưa bao giờ bỏ cuộc, nhưng nếu không có bạn, có lẽ dự án này sẽ mất hàng năm trời.</t>
         </is>
       </c>
     </row>
@@ -28663,7 +28663,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>"Trước khi vào Đài Quan Sát, Sephira lúc nào cũng ở bên ta. Lúc ta còn ở Học Viện, cô ấy đã chăm sóc ta. Mọi thủ tục giấy tờ cũng do cô ấy lo cả đấy," Dhalifa kể!</t>
+          <t>"Trước khi vào Đài Quan Sát, Sephira lúc nào cũng ở bên tao. Lúc tao còn ở Học Viện, cô ấy đã chăm sóc tao. Mọi thủ tục giấy tờ cũng do cô ấy lo cả đấy," Dhalifa kể!</t>
         </is>
       </c>
     </row>
@@ -28923,7 +28923,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Of course. Người Roya là dân bản địa của Lahai-Roi. Nếu không có họ giúp đỡ, Tập Thể chẳng thể nghiên cứu được một nửa những gì đang làm ở đây, và mỗi ngày chúng ta vẫn học được thêm điều mới từ họ.</t>
+          <t>Tất nhiên rồi. Người Roya là dân bản địa của Lahai-Roi. Nếu không có họ giúp đỡ, Tập Thể chẳng thể nghiên cứu được một nửa những gì đang làm ở đây, và mỗi ngày chúng ta vẫn học được thêm điều mới từ họ.</t>
         </is>
       </c>
     </row>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>"Bình tĩnh nào, Rakosan. Công tác chuẩn bị của chúng ta hoàn hảo mà. Đây không phải lỗi kỹ thuật đâu. Chắc chắn có điều gì khác đã xảy ra. Để Talkie kết nối với Terminal và chạy chẩn đoán toàn bộ đã," Dhalifa nói!</t>
+          <t>"Bình tĩnh nào, Rakosan. Công tác chuẩn bị của chúng ta hoàn hảo mà. Đây không phải lỗi kỹ thuật đâu. Chắc chắn có điều gì khác đã xảy ra. Để Talkie kết nối với Thiết bị đầu cuối và chạy chẩn đoán toàn bộ đã," Dhalifa nói!</t>
         </is>
       </c>
     </row>
@@ -29248,7 +29248,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>…Tôi biết. Tôi luôn biết. Mọi Roya đều hiểu cơn Void Storm đáng sợ đến nhường nào. Và tôi hiểu hơn ai hết Dhalifa và Tập thể Spacetrek đã chiến đấu chống lại nó khốc liệt ra sao.</t>
+          <t>…Tôi biết. Tôi luôn biết. Mọi Roya đều hiểu cơn Bão Hư Không đáng sợ đến nhường nào. Và tôi hiểu hơn ai hết Dhalifa và Tập thể Spacetrek đã chiến đấu chống lại nó khốc liệt ra sao.</t>
         </is>
       </c>
     </row>
@@ -29638,7 +29638,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>"Tớ đã Dodge chuyện giữa tớ và Sephira suốt. Sau tất cả những gì cô ấy đã làm cho tớ, tớ sợ nhắc đến chuyện đó sẽ chỉ khiến cô ấy tổn thương. Thật may là cậu đã nhẹ nhàng thúc đẩy chúng tớ. Cuối cùng chúng tớ cũng đã giải quyết được mọi chuyện," Dhalifa nói!</t>
+          <t>"Tớ đã né tránh chuyện giữa tớ và Sephira suốt. Sau tất cả những gì cô ấy đã làm cho tớ, tớ sợ nhắc đến chuyện đó sẽ chỉ khiến cô ấy tổn thương. Thật may là cậu đã nhẹ nhàng thúc đẩy chúng tớ. Cuối cùng chúng tớ cũng đã giải quyết được mọi chuyện," Dhalifa nói!</t>
         </is>
       </c>
     </row>
@@ -29898,7 +29898,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Nhìn kìa, đằng kia! Đó là Exoswarm của Sephira. Hồi nhỏ, tụi mình thường cưỡi chúng đi khắp nơi. Cô ấy đặc biệt thích bị Dodgem lên không bởi những con tuần lộc cơ khí!</t>
+          <t>Nhìn kìa, đằng kia! Đó là Exoswarm của Sephira. Hồi nhỏ, tụi mình thường cưỡi chúng đi khắp nơi. Cô ấy đặc biệt thích bị ném lên không bởi những con tuần lộc cơ khí!</t>
         </is>
       </c>
     </row>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory đã được tái thiết hoàn toàn. Chức năng khảo sát và ghi nhận của Lahai-Roi đã hoạt động trở lại. Đóng góp của ngươi thật sự phi thường. Hội Spacetrek Collective sẽ mãi tôn vinh công lao của ngươi!</t>
+          <t>Đài Quan Sát Spacetrek đã được tái thiết hoàn toàn. Chức năng khảo sát và ghi nhận của Lahai-Roi đã hoạt động trở lại. Đóng góp của ngươi thật sự phi thường. Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -30288,7 +30288,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>"Cảm ơn đã cứu Talkie. Tớ là Dhalifa, từng là thành viên đội vận hành của Đài quan sát Spacetrek. Giờ tớ đang cùng Rakosan xây dựng lại nơi này," Dhalifa nói với vẻ hồ hởi!</t>
+          <t>"Cảm ơn cậu đã cứu Talkie. Tớ là Dhalifa, từng là thành viên đội vận hành của Đài quan sát Spacetrek. Giờ tớ đang cùng Rakosan xây dựng lại nơi này," Dhalifa nói với vẻ hồ hởi!</t>
         </is>
       </c>
     </row>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Trước đây có vài người trong làng từng là Kẻ Bị Ruồng Bỏ. Sau này họ chuộc lỗi, nhưng mấy thứ này vẫn bị bỏ lại. Ta giữ lại phòng khi cần, rồi học cách dùng luôn. Cuối cùng cũng phát huy tác dụng rồi.</t>
+          <t>Trước đây có vài người trong làng từng là Kẻ Bị Ruồng Bỏ. Sau này họ chuộc lỗi, nhưng mấy thứ này vẫn bị bỏ lại. Tao giữ lại phòng khi cần, rồi học cách dùng luôn. Cuối cùng cũng phát huy tác dụng rồi.</t>
         </is>
       </c>
     </row>
@@ -30873,7 +30873,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Cậu thật chu đáo. Như cậu nói, những người đã mất trong Void Storm xứng đáng được tưởng nhớ, nhưng ký ức không nhất thiết phải toàn bi thương. Có lẽ cậu nên nói chuyện với Dhalifa về chuyện này.</t>
+          <t>Cậu thật chu đáo. Như cậu nói, những người đã mất trong Bão Hư Không xứng đáng được tưởng nhớ, nhưng ký ức không nhất thiết phải toàn bi thương. Có lẽ cậu nên nói chuyện với Dhalifa về chuyện này.</t>
         </is>
       </c>
     </row>
@@ -30938,7 +30938,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Nhưng không phải tất cả đều là nỗi buồn. Giống như Spacetrek Observatory ghi lại cả ánh sáng lẫn bóng tối, chúng ta cũng nên nhớ đến niềm vui của họ, và truyền lại những kỷ niệm đó cho những người đến sau này.</t>
+          <t>Nhưng không phải tất cả đều là nỗi buồn. Giống như Đài Thiên Văn Spacetrek ghi lại cả ánh sáng lẫn bóng tối, chúng ta cũng nên nhớ đến niềm vui của họ, và truyền lại những kỷ niệm đó cho những người đến sau này.</t>
         </is>
       </c>
     </row>
@@ -31328,7 +31328,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Kể từ đó, mọi người buộc phải đi đường vòng dài gấp mấy lần con đường cũ chỉ để tránh Void Storm. Với những chuyến giao hàng gấp, điều đó có nghĩa là phải chạy đua không ngừng nghỉ qua con đường vòng ấy.</t>
+          <t>Kể từ đó, mọi người buộc phải đi đường vòng dài gấp mấy lần con đường cũ chỉ để tránh Bão Hư Không. Với những chuyến giao hàng gấp, điều đó có nghĩa là phải chạy đua không ngừng nghỉ qua con đường vòng ấy.</t>
         </is>
       </c>
     </row>
@@ -31393,7 +31393,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tôi và đồng nghiệp đang tái thiết mạng lưới tuyến đường đã sụp đổ khắp Etching Plains. Với tiến độ gần đây, cuối cùng chúng tôi cũng lên kế hoạch cho bước tiếp theo… nhưng lại thiếu người thử nghiệm.</t>
+          <t>Tôi và đồng nghiệp đang tái thiết mạng lưới tuyến đường đã sụp đổ khắp Đồng Bằng Khắc Tạc. Với tiến độ gần đây, cuối cùng chúng tôi cũng lên kế hoạch cho bước tiếp theo… nhưng lại thiếu người thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -31458,7 +31458,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Ta từng nghĩ công việc này... chỉ là chuyện vặt vãnh so với nghiên cứu về Exostrider của ta. Nhưng thấy nó thực sự cải thiện cuộc sống của mọi người khiến ta thực sự vui.</t>
+          <t>Tao từng nghĩ công việc này... chỉ là chuyện vặt vãnh so với nghiên cứu về Exostrider của tao. Nhưng thấy nó thực sự cải thiện cuộc sống của mọi người khiến tao thực sự vui.</t>
         </is>
       </c>
     </row>
@@ -31588,7 +31588,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>"Anh ấy không hề nổi giận. Thay vào đó, anh còn chậm nhịp hơn, kiên nhẫn dẫn dắt chúng tôi. Melody trôi trong không khí như dòng nước biển, và cùng với nó, chúng tôi di chuyển như những chú cá bay vậy."</t>
+          <t>"Anh ấy không hề nổi giận. Thay vào đó, anh còn chậm nhịp hơn, kiên nhẫn dẫn dắt chúng tôi. Giai điệu trôi trong không khí như dòng nước biển, và cùng với nó, chúng tôi di chuyển như những chú cá bay vậy."</t>
         </is>
       </c>
     </row>
@@ -31978,7 +31978,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>"Right rồi. Trước khi chia tay, Matthew đã đưa chúng ta đến nơi cao nhất, nơi đàn cá bay sinh sống. Cậu ấy muốn chúng ta thấy giai điệu mà ta cùng tạo ra trôi theo gió, và làm sao nó nâng những con cá bay lên bầu trời."</t>
+          <t>"Phải rồi. Trước khi chia tay, Matthew đã đưa chúng ta đến nơi cao nhất, nơi đàn cá bay sinh sống. Cậu ấy muốn chúng ta thấy giai điệu mà ta cùng tạo ra trôi theo gió, và làm sao nó nâng những con cá bay lên bầu trời."</t>
         </is>
       </c>
     </row>
@@ -32888,7 +32888,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>"Hồi đó, dù mới ở cùng Matthew được một thời gian ngắn, Do và Re lại nhớ thứ tự tốt hơn ta. Còn ta thì cứ nhầm hoài, bắt mọi người phải bắt đầu lại hết lần này đến lần khác…"</t>
+          <t>"Hồi đó, dù mới ở cùng Matthew được một thời gian ngắn, Do và Re lại nhớ thứ tự tốt hơn tao. Còn tao thì cứ nhầm hoài, bắt mọi người phải bắt đầu lại hết lần này đến lần khác…"</t>
         </is>
       </c>
     </row>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Gửi tọa độ của Terminal Huấn luyện Xe. Hãy vận hành phương tiện sau khi đã nghiên cứu kỹ hướng dẫn điều khiển và nắm vững Quy định An toàn Giao thông.</t>
+          <t>Gửi tọa độ của Thiết bị đầu cuối Huấn luyện Xe. Hãy vận hành phương tiện sau khi đã nghiên cứu kỹ hướng dẫn điều khiển và nắm vững Quy định An toàn Giao thông.</t>
         </is>
       </c>
     </row>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Gửi tọa độ của Terminal Huấn luyện Xe. Hãy vận hành phương tiện sau khi đã nghiên cứu kỹ hướng dẫn điều khiển và nắm vững Quy định An toàn Giao thông.</t>
+          <t>Gửi tọa độ của Thiết bị đầu cuối Huấn luyện Xe. Hãy vận hành phương tiện sau khi đã nghiên cứu kỹ hướng dẫn điều khiển và nắm vững Quy định An toàn Giao thông.</t>
         </is>
       </c>
     </row>
